--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -17196,6 +17196,9 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Söder om Kvarntjärn, Söder om Kvarntjärn, Pi lm</t>
@@ -17256,6 +17259,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -17270,7 +17274,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -19743,7 +19743,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Äldre ringhack bild</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Christina Boyd, Martin Axegård, Jörgen Sundin, Benny Öwre, per-erik mukka, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Alva Danielsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Elin Kannerby, anders tedeholm, Alva Danielsson, Alva Dahlqvist Cederstrand, Ulrika Karlsson, per-erik mukka, Benny Öwre, Jörgen Sundin, Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Ulrika Karlsson, Jörgen Sundin, Alva Dahlqvist Cederstrand, Alva Danielsson, Martin Axegård, Tyr Nilsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Benny Öwre</t>
+          <t>Christina Boyd, Benny Öwre, Anton Lundberg, Elin Kannerby, anders tedeholm, Tyr Nilsson, Martin Axegård, Alva Danielsson, Alva Dahlqvist Cederstrand, Jörgen Sundin, Ulrika Karlsson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Martin Axegård, anders tedeholm, Benny Öwre, Ulrika Karlsson</t>
+          <t>Christina Boyd, Ulrika Karlsson, Benny Öwre, anders tedeholm, Martin Axegård, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AZ189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303115</t>
         </is>
       </c>
     </row>
@@ -1117,6 +1137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297950</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295629</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295622</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294740</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295289</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295633</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294737</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294739</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294741</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295620</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295631</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297947</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2565,6 +2650,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302464</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295586</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2785,6 +2880,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297952</t>
         </is>
       </c>
     </row>
@@ -2902,6 +3002,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294249</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297946</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3124,6 +3234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298730</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3235,6 +3350,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295584</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3347,6 +3467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294559</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3458,6 +3583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295623</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3569,6 +3699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298729</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3676,6 +3811,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302465</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3783,6 +3923,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302470</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3894,6 +4039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303107</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4005,6 +4155,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303112</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4114,6 +4269,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295632</t>
         </is>
       </c>
     </row>
@@ -4230,6 +4390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293580</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4345,6 +4510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294246</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4460,6 +4630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294560</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4571,6 +4746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294735</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4682,6 +4862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294738</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4793,6 +4978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295290</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4904,6 +5094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295619</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5015,6 +5210,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295625</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5126,6 +5326,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297948</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5237,6 +5442,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297951</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5348,6 +5558,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297953</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5460,6 +5675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298731</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5571,6 +5791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295621</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5682,6 +5907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295627</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5789,6 +6019,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302471</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5909,6 +6144,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302466</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6026,6 +6266,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302468</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6137,6 +6382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298728</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6248,6 +6498,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298732</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6360,6 +6615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295624</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6470,6 +6730,11 @@
       <c r="AY53" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295626</t>
         </is>
       </c>
     </row>
@@ -6587,6 +6852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294561</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6698,6 +6968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295628</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6807,6 +7082,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295630</t>
         </is>
       </c>
     </row>
@@ -6924,6 +7204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303108</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7035,6 +7320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303113</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7144,6 +7434,11 @@
       <c r="AY59" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303111</t>
         </is>
       </c>
     </row>
@@ -7261,6 +7556,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294558</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7376,6 +7676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294562</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7485,6 +7790,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294734</t>
         </is>
       </c>
     </row>
@@ -7602,6 +7912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294556</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7713,6 +8028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295615</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7824,6 +8144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295616</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7935,6 +8260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295617</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8042,6 +8372,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302472</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8149,6 +8484,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302478</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8260,6 +8600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298726</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8371,6 +8716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295287</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8482,6 +8832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295614</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8594,6 +8949,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302474</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8705,6 +9065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298727</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8812,6 +9177,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302476</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8919,6 +9289,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302479</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9028,6 +9403,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297929</t>
         </is>
       </c>
     </row>
@@ -9144,6 +9524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293571</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9259,6 +9644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294542</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9374,6 +9764,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294551</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9489,6 +9884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294553</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9600,6 +10000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295605</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9711,6 +10116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295610</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9820,6 +10230,11 @@
       <c r="AY83" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295582</t>
         </is>
       </c>
     </row>
@@ -9937,6 +10352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294545</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10051,6 +10471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293572</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10162,6 +10587,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295575</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10274,6 +10704,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295603</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10381,6 +10816,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302490</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10496,6 +10936,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296757</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10610,6 +11055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293568</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10721,6 +11171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303129</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10830,6 +11285,11 @@
       <c r="AY92" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303132</t>
         </is>
       </c>
     </row>
@@ -10946,6 +11406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293570</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11061,6 +11526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294234</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11176,6 +11646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294544</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11287,6 +11762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295281</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11398,6 +11878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295609</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11509,6 +11994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295612</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11616,6 +12106,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302487</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11727,6 +12222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303128</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11834,6 +12334,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302491</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11948,6 +12453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293569</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12063,6 +12573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294227</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12178,6 +12693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294232</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12293,6 +12813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294546</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12404,6 +12929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295283</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12513,6 +13043,11 @@
       <c r="AY107" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295611</t>
         </is>
       </c>
     </row>
@@ -12630,6 +13165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296754</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12741,6 +13281,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297927</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12852,6 +13397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298723</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12959,6 +13509,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302489</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13066,6 +13621,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302493</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13177,6 +13737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297925</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13288,6 +13853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297928</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13395,6 +13965,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302494</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13510,6 +14085,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294554</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13625,6 +14205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296755</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13736,6 +14321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297943</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13855,6 +14445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293566</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13974,6 +14569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293583</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14093,6 +14693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293584</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14212,6 +14817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293585</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14331,6 +14941,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293586</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14450,6 +15065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293587</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14574,6 +15194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297954</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14688,6 +15313,11 @@
       <c r="AY126" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298724</t>
         </is>
       </c>
     </row>
@@ -14806,6 +15436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294226</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14917,6 +15552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295286</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15026,6 +15666,11 @@
       <c r="AY129" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303130</t>
         </is>
       </c>
     </row>
@@ -15143,6 +15788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294547</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15254,6 +15904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294730</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15365,6 +16020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295599</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15476,6 +16136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297924</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15583,6 +16248,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302481</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15697,6 +16367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293567</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15808,6 +16483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295600</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15924,6 +16604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298722</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16033,6 +16718,11 @@
       <c r="AY138" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303131</t>
         </is>
       </c>
     </row>
@@ -16150,6 +16840,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294548</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16265,6 +16960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294552</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16376,6 +17076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303116</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16487,6 +17192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303118</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16596,6 +17306,11 @@
       <c r="AY143" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297942</t>
         </is>
       </c>
     </row>
@@ -16712,6 +17427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293577</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16821,6 +17541,11 @@
       <c r="AY145" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295580</t>
         </is>
       </c>
     </row>
@@ -16938,6 +17663,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294242</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17053,6 +17783,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294245</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17162,6 +17897,11 @@
       <c r="AY148" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303117</t>
         </is>
       </c>
     </row>
@@ -17279,6 +18019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135304947</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17393,6 +18138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293573</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17508,6 +18258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294236</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17623,6 +18378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294243</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17738,6 +18498,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294549</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17849,6 +18614,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303127</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17956,6 +18726,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302485</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18066,6 +18841,11 @@
       <c r="AY156" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303124</t>
         </is>
       </c>
     </row>
@@ -18182,6 +18962,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293576</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18296,6 +19081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293578</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18403,6 +19193,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294235</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18518,6 +19313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294244</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18633,6 +19433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294550</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18748,6 +19553,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294555</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18859,6 +19669,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295285</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18970,6 +19785,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297931</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19081,6 +19901,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297939</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19192,6 +20017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297945</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19299,6 +20129,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302486</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19410,6 +20245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303126</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19526,6 +20366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297944</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19647,6 +20492,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294729</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19771,6 +20621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297936</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19895,6 +20750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297937</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20015,6 +20875,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302457</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20131,6 +20996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298725</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20242,6 +21112,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297938</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20370,6 +21245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297940</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20486,6 +21366,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302482</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20602,6 +21487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293575</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20713,6 +21603,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295576</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20820,6 +21715,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294238</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20936,6 +21836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294240</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21047,6 +21952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295608</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21158,6 +22068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297932</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21269,6 +22184,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294732</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21376,6 +22296,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302480</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21487,6 +22412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303120</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21598,6 +22528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303121</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21709,6 +22644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303123</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21820,8 +22760,203 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Elin Kannerby, anders tedeholm, Alva Danielsson, Alva Dahlqvist Cederstrand, Ulrika Karlsson, per-erik mukka, Benny Öwre, Jörgen Sundin, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Jörgen Sundin, Benny Öwre, per-erik mukka, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Alva Danielsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Christina Boyd, Benny Öwre, Anton Lundberg, Elin Kannerby, anders tedeholm, Tyr Nilsson, Martin Axegård, Alva Danielsson, Alva Dahlqvist Cederstrand, Jörgen Sundin, Ulrika Karlsson, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Ulrika Karlsson, Jörgen Sundin, Alva Dahlqvist Cederstrand, Alva Danielsson, Martin Axegård, Tyr Nilsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Benny Öwre</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Christina Boyd, Ulrika Karlsson, Benny Öwre, anders tedeholm, Martin Axegård, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Martin Axegård, anders tedeholm, Benny Öwre, Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård, Christina Boyd, anders tedeholm, Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135303115</v>
       </c>
       <c r="B4" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>135297950</v>
       </c>
       <c r="B5" t="n">
-        <v>92235</v>
+        <v>92277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>135295629</v>
       </c>
       <c r="B6" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135295622</v>
       </c>
       <c r="B7" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135294740</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård, Christina Boyd, anders tedeholm, Ulrika Karlsson</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1505,7 +1505,7 @@
         <v>135295289</v>
       </c>
       <c r="B9" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1621,7 +1621,7 @@
         <v>135303106</v>
       </c>
       <c r="B10" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135295633</v>
       </c>
       <c r="B11" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135294737</v>
       </c>
       <c r="B12" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135294739</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135294741</v>
       </c>
       <c r="B14" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135295620</v>
       </c>
       <c r="B15" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135295631</v>
       </c>
       <c r="B16" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135297947</v>
       </c>
       <c r="B17" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135302464</v>
       </c>
       <c r="B18" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135295586</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135297952</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>135294249</v>
       </c>
       <c r="B21" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135297946</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135298730</v>
       </c>
       <c r="B23" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135295584</v>
       </c>
       <c r="B24" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135294559</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135295623</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135298729</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>135302465</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135302470</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135303107</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>135303112</v>
       </c>
       <c r="B31" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>135295632</v>
       </c>
       <c r="B32" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135293580</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135294246</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135294560</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>135294735</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4757,7 +4757,7 @@
         <v>135294738</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4873,7 +4873,7 @@
         <v>135295290</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>135295619</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135295625</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>135297948</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>135297951</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>135297953</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>135298731</v>
       </c>
       <c r="B44" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>135295621</v>
       </c>
       <c r="B45" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>135295627</v>
       </c>
       <c r="B46" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>135302471</v>
       </c>
       <c r="B47" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135302466</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135302468</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>135298728</v>
       </c>
       <c r="B50" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>135298732</v>
       </c>
       <c r="B51" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135295624</v>
       </c>
       <c r="B52" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>135295626</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>135294561</v>
       </c>
       <c r="B54" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>135295628</v>
       </c>
       <c r="B55" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>135295630</v>
       </c>
       <c r="B56" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>135303108</v>
       </c>
       <c r="B57" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>135303113</v>
       </c>
       <c r="B58" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>135303111</v>
       </c>
       <c r="B59" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>135294558</v>
       </c>
       <c r="B60" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>135294562</v>
       </c>
       <c r="B61" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>135294734</v>
       </c>
       <c r="B62" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7803,7 +7803,7 @@
         <v>135294556</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135295615</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>135295616</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>135295617</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135302472</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>135302478</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135298726</v>
       </c>
       <c r="B69" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135295287</v>
       </c>
       <c r="B70" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135295614</v>
       </c>
       <c r="B71" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>135302474</v>
       </c>
       <c r="B72" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135298727</v>
       </c>
       <c r="B73" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135302476</v>
       </c>
       <c r="B74" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>135302479</v>
       </c>
       <c r="B75" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>135297929</v>
       </c>
       <c r="B76" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>135293571</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135294542</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>135294551</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>135294553</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>135295605</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>135295610</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>135295582</v>
       </c>
       <c r="B83" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>135294545</v>
       </c>
       <c r="B84" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>135293572</v>
       </c>
       <c r="B85" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>135295575</v>
       </c>
       <c r="B86" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>135295603</v>
       </c>
       <c r="B87" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135302490</v>
       </c>
       <c r="B88" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>135296757</v>
       </c>
       <c r="B89" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>135293568</v>
       </c>
       <c r="B90" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>135303129</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>135303132</v>
       </c>
       <c r="B92" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>135293570</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>135294234</v>
       </c>
       <c r="B94" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>135294544</v>
       </c>
       <c r="B95" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>135295281</v>
       </c>
       <c r="B96" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11773,7 +11773,7 @@
         <v>135295609</v>
       </c>
       <c r="B97" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>135295612</v>
       </c>
       <c r="B98" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>135302487</v>
       </c>
       <c r="B99" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>135303128</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>135302491</v>
       </c>
       <c r="B101" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>135293569</v>
       </c>
       <c r="B102" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>135294227</v>
       </c>
       <c r="B103" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>135294232</v>
       </c>
       <c r="B104" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>135294546</v>
       </c>
       <c r="B105" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>135295283</v>
       </c>
       <c r="B106" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12940,7 +12940,7 @@
         <v>135295611</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>135296754</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135297927</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>135298723</v>
       </c>
       <c r="B110" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>135302489</v>
       </c>
       <c r="B111" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>135302493</v>
       </c>
       <c r="B112" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>135297925</v>
       </c>
       <c r="B113" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>135297928</v>
       </c>
       <c r="B114" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>135302494</v>
       </c>
       <c r="B115" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>135294554</v>
       </c>
       <c r="B116" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>135296755</v>
       </c>
       <c r="B117" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>135297943</v>
       </c>
       <c r="B118" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>135293566</v>
       </c>
       <c r="B119" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>135293583</v>
       </c>
       <c r="B120" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>135293584</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>135293585</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>135293586</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>135293587</v>
       </c>
       <c r="B124" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>135297954</v>
       </c>
       <c r="B125" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>135298724</v>
       </c>
       <c r="B126" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>135294226</v>
       </c>
       <c r="B127" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135295286</v>
       </c>
       <c r="B128" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>135303130</v>
       </c>
       <c r="B129" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>135294547</v>
       </c>
       <c r="B130" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>135294730</v>
       </c>
       <c r="B131" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>135295599</v>
       </c>
       <c r="B132" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135297924</v>
       </c>
       <c r="B133" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>135302481</v>
       </c>
       <c r="B134" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>135293567</v>
       </c>
       <c r="B135" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>135295600</v>
       </c>
       <c r="B136" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135298722</v>
       </c>
       <c r="B137" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>135303131</v>
       </c>
       <c r="B138" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>135294548</v>
       </c>
       <c r="B139" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>135294552</v>
       </c>
       <c r="B140" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>135303116</v>
       </c>
       <c r="B141" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>135303118</v>
       </c>
       <c r="B142" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>135297942</v>
       </c>
       <c r="B143" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>135293577</v>
       </c>
       <c r="B144" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>135295580</v>
       </c>
       <c r="B145" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>135294242</v>
       </c>
       <c r="B146" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>135294245</v>
       </c>
       <c r="B147" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>135303117</v>
       </c>
       <c r="B148" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>135304947</v>
       </c>
       <c r="B149" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>135293573</v>
       </c>
       <c r="B150" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>135294236</v>
       </c>
       <c r="B151" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>135294243</v>
       </c>
       <c r="B152" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>135294549</v>
       </c>
       <c r="B153" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>135303127</v>
       </c>
       <c r="B154" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>135302485</v>
       </c>
       <c r="B155" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>135303124</v>
       </c>
       <c r="B156" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>135293576</v>
       </c>
       <c r="B157" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>135293578</v>
       </c>
       <c r="B158" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>135294235</v>
       </c>
       <c r="B159" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>135294244</v>
       </c>
       <c r="B160" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>135294550</v>
       </c>
       <c r="B161" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>135294555</v>
       </c>
       <c r="B162" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>135295285</v>
       </c>
       <c r="B163" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>135297931</v>
       </c>
       <c r="B164" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>135297939</v>
       </c>
       <c r="B165" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>135297945</v>
       </c>
       <c r="B166" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>135302486</v>
       </c>
       <c r="B167" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>135303126</v>
       </c>
       <c r="B168" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>135297944</v>
       </c>
       <c r="B169" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>135294729</v>
       </c>
       <c r="B170" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>135297936</v>
       </c>
       <c r="B171" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>135297937</v>
       </c>
       <c r="B172" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>135302457</v>
       </c>
       <c r="B173" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>135298725</v>
       </c>
       <c r="B174" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>135297938</v>
       </c>
       <c r="B175" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>135297940</v>
       </c>
       <c r="B176" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>135302482</v>
       </c>
       <c r="B177" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>135293575</v>
       </c>
       <c r="B178" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>135295576</v>
       </c>
       <c r="B179" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>135294238</v>
       </c>
       <c r="B180" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>135294240</v>
       </c>
       <c r="B181" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>135295608</v>
       </c>
       <c r="B182" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>135297932</v>
       </c>
       <c r="B183" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>135294732</v>
       </c>
       <c r="B184" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>135302480</v>
       </c>
       <c r="B185" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>135303120</v>
       </c>
       <c r="B186" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>135303121</v>
       </c>
       <c r="B187" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>135303123</v>
       </c>
       <c r="B188" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>135303125</v>
       </c>
       <c r="B189" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135303115</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>135297950</v>
       </c>
       <c r="B5" t="n">
-        <v>92277</v>
+        <v>92304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>135295629</v>
       </c>
       <c r="B6" t="n">
-        <v>83393</v>
+        <v>83420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135295622</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135294740</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135295289</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135303106</v>
       </c>
       <c r="B10" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135295633</v>
       </c>
       <c r="B11" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135294737</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135294739</v>
       </c>
       <c r="B13" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135294741</v>
       </c>
       <c r="B14" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135295620</v>
       </c>
       <c r="B15" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135295631</v>
       </c>
       <c r="B16" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135297947</v>
       </c>
       <c r="B17" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135302464</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135295586</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135297952</v>
       </c>
       <c r="B20" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>135294249</v>
       </c>
       <c r="B21" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135297946</v>
       </c>
       <c r="B22" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135298730</v>
       </c>
       <c r="B23" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135295584</v>
       </c>
       <c r="B24" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135294559</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135295623</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135298729</v>
       </c>
       <c r="B27" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>135302465</v>
       </c>
       <c r="B28" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135302470</v>
       </c>
       <c r="B29" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135303107</v>
       </c>
       <c r="B30" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>135303112</v>
       </c>
       <c r="B31" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>135295632</v>
       </c>
       <c r="B32" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135293580</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135294246</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135294560</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>135294735</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>135294738</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>135295290</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>135295619</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135295625</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>135297948</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>135297951</v>
       </c>
       <c r="B42" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>135297953</v>
       </c>
       <c r="B43" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>135298731</v>
       </c>
       <c r="B44" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>135295621</v>
       </c>
       <c r="B45" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>135295627</v>
       </c>
       <c r="B46" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>135302471</v>
       </c>
       <c r="B47" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>135298728</v>
       </c>
       <c r="B50" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>135298732</v>
       </c>
       <c r="B51" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135295624</v>
       </c>
       <c r="B52" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>135295626</v>
       </c>
       <c r="B53" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>135294561</v>
       </c>
       <c r="B54" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>135295628</v>
       </c>
       <c r="B55" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>135295630</v>
       </c>
       <c r="B56" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>135303108</v>
       </c>
       <c r="B57" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>135303113</v>
       </c>
       <c r="B58" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>135303111</v>
       </c>
       <c r="B59" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>135294558</v>
       </c>
       <c r="B60" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>135294562</v>
       </c>
       <c r="B61" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>135294734</v>
       </c>
       <c r="B62" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>135294556</v>
       </c>
       <c r="B63" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135295615</v>
       </c>
       <c r="B64" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>135295616</v>
       </c>
       <c r="B65" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>135295617</v>
       </c>
       <c r="B66" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135302472</v>
       </c>
       <c r="B67" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>135302478</v>
       </c>
       <c r="B68" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135298726</v>
       </c>
       <c r="B69" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135295287</v>
       </c>
       <c r="B70" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135295614</v>
       </c>
       <c r="B71" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135298727</v>
       </c>
       <c r="B73" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135302476</v>
       </c>
       <c r="B74" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>135302479</v>
       </c>
       <c r="B75" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>135297929</v>
       </c>
       <c r="B76" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>135293571</v>
       </c>
       <c r="B77" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135294542</v>
       </c>
       <c r="B78" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>135294551</v>
       </c>
       <c r="B79" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>135294553</v>
       </c>
       <c r="B80" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>135295605</v>
       </c>
       <c r="B81" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>135295610</v>
       </c>
       <c r="B82" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>135295582</v>
       </c>
       <c r="B83" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>135294545</v>
       </c>
       <c r="B84" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>135293572</v>
       </c>
       <c r="B85" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>135295575</v>
       </c>
       <c r="B86" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>135295603</v>
       </c>
       <c r="B87" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135302490</v>
       </c>
       <c r="B88" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>135296757</v>
       </c>
       <c r="B89" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>135293568</v>
       </c>
       <c r="B90" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>135303129</v>
       </c>
       <c r="B91" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>135303132</v>
       </c>
       <c r="B92" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>135293570</v>
       </c>
       <c r="B93" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>135294234</v>
       </c>
       <c r="B94" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>135294544</v>
       </c>
       <c r="B95" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>135295281</v>
       </c>
       <c r="B96" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>135295609</v>
       </c>
       <c r="B97" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>135295612</v>
       </c>
       <c r="B98" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>135302487</v>
       </c>
       <c r="B99" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>135303128</v>
       </c>
       <c r="B100" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>135302491</v>
       </c>
       <c r="B101" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>135293569</v>
       </c>
       <c r="B102" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>135294227</v>
       </c>
       <c r="B103" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>135294232</v>
       </c>
       <c r="B104" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>135294546</v>
       </c>
       <c r="B105" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>135295283</v>
       </c>
       <c r="B106" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>135295611</v>
       </c>
       <c r="B107" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>135296754</v>
       </c>
       <c r="B108" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135297927</v>
       </c>
       <c r="B109" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>135298723</v>
       </c>
       <c r="B110" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>135302489</v>
       </c>
       <c r="B111" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>135302493</v>
       </c>
       <c r="B112" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>135297925</v>
       </c>
       <c r="B113" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>135297928</v>
       </c>
       <c r="B114" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>135302494</v>
       </c>
       <c r="B115" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>135294554</v>
       </c>
       <c r="B116" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>135296755</v>
       </c>
       <c r="B117" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>135297943</v>
       </c>
       <c r="B118" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>135294226</v>
       </c>
       <c r="B127" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135295286</v>
       </c>
       <c r="B128" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>135303130</v>
       </c>
       <c r="B129" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>135294547</v>
       </c>
       <c r="B130" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>135294730</v>
       </c>
       <c r="B131" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>135295599</v>
       </c>
       <c r="B132" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135297924</v>
       </c>
       <c r="B133" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>135302481</v>
       </c>
       <c r="B134" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>135293567</v>
       </c>
       <c r="B135" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>135295600</v>
       </c>
       <c r="B136" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135298722</v>
       </c>
       <c r="B137" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>135303131</v>
       </c>
       <c r="B138" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>135294548</v>
       </c>
       <c r="B139" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>135294552</v>
       </c>
       <c r="B140" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>135303116</v>
       </c>
       <c r="B141" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>135303118</v>
       </c>
       <c r="B142" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>135297942</v>
       </c>
       <c r="B143" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>135293577</v>
       </c>
       <c r="B144" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>135295580</v>
       </c>
       <c r="B145" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>135294242</v>
       </c>
       <c r="B146" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>135294245</v>
       </c>
       <c r="B147" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>135303117</v>
       </c>
       <c r="B148" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>135304947</v>
       </c>
       <c r="B149" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>135293573</v>
       </c>
       <c r="B150" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>135294236</v>
       </c>
       <c r="B151" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>135294243</v>
       </c>
       <c r="B152" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>135294549</v>
       </c>
       <c r="B153" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>135303127</v>
       </c>
       <c r="B154" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>135302485</v>
       </c>
       <c r="B155" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>135303124</v>
       </c>
       <c r="B156" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>135293576</v>
       </c>
       <c r="B157" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>135293578</v>
       </c>
       <c r="B158" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>135294235</v>
       </c>
       <c r="B159" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>135294244</v>
       </c>
       <c r="B160" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>135294550</v>
       </c>
       <c r="B161" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>135294555</v>
       </c>
       <c r="B162" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>135295285</v>
       </c>
       <c r="B163" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>135297931</v>
       </c>
       <c r="B164" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>135297939</v>
       </c>
       <c r="B165" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>135297945</v>
       </c>
       <c r="B166" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>135302486</v>
       </c>
       <c r="B167" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>135303126</v>
       </c>
       <c r="B168" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>135297944</v>
       </c>
       <c r="B169" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>135294238</v>
       </c>
       <c r="B180" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>135294240</v>
       </c>
       <c r="B181" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>135295608</v>
       </c>
       <c r="B182" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>135297932</v>
       </c>
       <c r="B183" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>135294732</v>
       </c>
       <c r="B184" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>135302480</v>
       </c>
       <c r="B185" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>135303120</v>
       </c>
       <c r="B186" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>135303121</v>
       </c>
       <c r="B187" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>135303123</v>
       </c>
       <c r="B188" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>135303125</v>
       </c>
       <c r="B189" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135303115</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>135297950</v>
       </c>
       <c r="B5" t="n">
-        <v>92309</v>
+        <v>92311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135295622</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135294740</v>
       </c>
       <c r="B8" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135295289</v>
       </c>
       <c r="B9" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135303106</v>
       </c>
       <c r="B10" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135294737</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135294739</v>
       </c>
       <c r="B13" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135294741</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135295620</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135295631</v>
       </c>
       <c r="B16" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135297947</v>
       </c>
       <c r="B17" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135302464</v>
       </c>
       <c r="B18" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135295586</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135297952</v>
       </c>
       <c r="B20" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>135294249</v>
       </c>
       <c r="B21" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135297946</v>
       </c>
       <c r="B22" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135298730</v>
       </c>
       <c r="B23" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135295584</v>
       </c>
       <c r="B24" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>135298728</v>
       </c>
       <c r="B50" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>135298732</v>
       </c>
       <c r="B51" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>135294734</v>
       </c>
       <c r="B62" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135298726</v>
       </c>
       <c r="B69" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135298727</v>
       </c>
       <c r="B73" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>135297929</v>
       </c>
       <c r="B76" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>135293572</v>
       </c>
       <c r="B85" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>135295575</v>
       </c>
       <c r="B86" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>135295603</v>
       </c>
       <c r="B87" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135302490</v>
       </c>
       <c r="B88" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>135296757</v>
       </c>
       <c r="B89" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>135293568</v>
       </c>
       <c r="B90" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>135294226</v>
       </c>
       <c r="B127" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135295286</v>
       </c>
       <c r="B128" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>135303130</v>
       </c>
       <c r="B129" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>135297942</v>
       </c>
       <c r="B143" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>135293577</v>
       </c>
       <c r="B144" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>135295580</v>
       </c>
       <c r="B145" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>135294238</v>
       </c>
       <c r="B180" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>135294240</v>
       </c>
       <c r="B181" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>135295608</v>
       </c>
       <c r="B182" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>135297932</v>
       </c>
       <c r="B183" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">

--- a/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure korsningen Långviken avvanm artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>135297950</v>
       </c>
       <c r="B5" t="n">
-        <v>92311</v>
+        <v>92325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>135297936</v>
       </c>
       <c r="B171" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
